--- a/public/plantilla-acciones-correctivas.xlsx
+++ b/public/plantilla-acciones-correctivas.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones Correctivas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="29">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,14 +75,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
@@ -165,14 +157,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <sz val="9.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="8.5"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -214,6 +198,44 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <sz val="7"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF1B2A45"/>
       <sz val="10"/>
     </font>
@@ -222,19 +244,66 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="8.5"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -246,18 +315,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
@@ -280,24 +337,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFEEF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
         <bgColor rgb="FFEEF1F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.0499893185216834"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCCF6A"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -427,10 +544,82 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9AA3B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9AA3B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9AA3B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9AA3B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9AA3B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color theme="3" tint="0.5999633777886288"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
       <top style="thin">
         <color theme="3" tint="0.5999633777886288"/>
       </top>
@@ -440,91 +629,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF9AA3B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF9AA3B2"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF9AA3B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF9AA3B2"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF9AA3B2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF9AA3B2"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF9AA3B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF9AA3B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9AA3B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </left>
-      <right style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0"/>
       </left>
@@ -536,8 +640,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color theme="3" tint="0.5999633777886288"/>
@@ -546,36 +665,182 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0"/>
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
       </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
       <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -583,7 +848,46 @@
       <left/>
       <right/>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -591,22 +895,123 @@
     <border>
       <left/>
       <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF9AA3B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF9AA3B2"/>
-      </right>
-      <top/>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -619,321 +1024,911 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -943,7 +1938,154 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF595959"/>
+          <bgColor rgb="FF595959"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7F4F24"/>
+          <bgColor rgb="FF7F4F24"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF57C00"/>
+          <bgColor rgb="FFF57C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -958,13 +2100,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
+      <xdr:colOff>676329</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
+      <xdr:rowOff>167468</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -974,7 +2116,13 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2808000" cy="1296000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1287,725 +2435,719 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="5" customWidth="1" style="70" min="1" max="1"/>
-    <col width="11" customWidth="1" style="70" min="2" max="2"/>
-    <col width="15" customWidth="1" style="70" min="3" max="3"/>
-    <col width="10" customWidth="1" style="70" min="4" max="4"/>
-    <col width="30" customWidth="1" style="70" min="5" max="5"/>
-    <col width="12" customWidth="1" style="70" min="6" max="6"/>
-    <col width="32" customWidth="1" style="70" min="7" max="7"/>
-    <col width="16" customWidth="1" style="70" min="8" max="8"/>
-    <col width="11" customWidth="1" style="70" min="9" max="9"/>
-    <col width="16" customWidth="1" style="70" min="10" max="10"/>
-    <col width="12" customWidth="1" style="70" min="11" max="11"/>
-    <col width="13" customWidth="1" style="70" min="12" max="12"/>
+    <col width="5" customWidth="1" style="127" min="1" max="1"/>
+    <col width="11" customWidth="1" style="127" min="2" max="2"/>
+    <col width="15" customWidth="1" style="127" min="3" max="3"/>
+    <col width="10" customWidth="1" style="127" min="4" max="4"/>
+    <col width="30" customWidth="1" style="127" min="5" max="5"/>
+    <col width="12" customWidth="1" style="127" min="6" max="6"/>
+    <col width="32" customWidth="1" style="127" min="7" max="7"/>
+    <col width="16" customWidth="1" style="127" min="8" max="8"/>
+    <col width="11" customWidth="1" style="127" min="9" max="9"/>
+    <col width="16" customWidth="1" style="127" min="10" max="10"/>
+    <col width="12" customWidth="1" style="127" min="11" max="11"/>
+    <col width="13" customWidth="1" style="127" min="12" max="12"/>
+    <col width="8.88671875" customWidth="1" style="127" min="13" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="70">
-      <c r="D1" s="35" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="127">
+      <c r="D1" s="221" t="n"/>
+      <c r="E1" s="214" t="inlineStr">
         <is>
           <t>ACCIONES CORRECTIVAS, PREVENTIVAS Y DE MEJORA</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" s="70">
-      <c r="D2" s="37" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-    </row>
-    <row r="3" ht="4.95" customHeight="1" s="70">
-      <c r="D3" s="75" t="n"/>
-      <c r="E3" s="56" t="n"/>
-      <c r="F3" s="56" t="n"/>
-      <c r="G3" s="56" t="n"/>
-      <c r="H3" s="56" t="n"/>
-      <c r="I3" s="56" t="n"/>
-      <c r="J3" s="56" t="n"/>
-      <c r="K3" s="56" t="n"/>
-      <c r="L3" s="56" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="70">
-      <c r="J4" s="53" t="inlineStr">
+    <row r="2" ht="14.4" customHeight="1" s="127">
+      <c r="D2" s="222" t="n"/>
+      <c r="E2" s="98" t="n"/>
+      <c r="F2" s="98" t="n"/>
+      <c r="G2" s="98" t="n"/>
+      <c r="H2" s="98" t="n"/>
+      <c r="I2" s="98" t="n"/>
+      <c r="J2" s="98" t="n"/>
+      <c r="K2" s="98" t="n"/>
+      <c r="L2" s="98" t="n"/>
+    </row>
+    <row r="3" ht="4.95" customHeight="1" s="127">
+      <c r="D3" s="221" t="n"/>
+      <c r="E3" s="60" t="n"/>
+      <c r="F3" s="104" t="n"/>
+      <c r="G3" s="104" t="n"/>
+      <c r="H3" s="104" t="n"/>
+      <c r="I3" s="104" t="n"/>
+      <c r="J3" s="104" t="n"/>
+      <c r="K3" s="104" t="n"/>
+      <c r="L3" s="104" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="127">
+      <c r="J4" s="139" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="31" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="70">
-      <c r="D5" s="40" t="inlineStr">
+      <c r="K4" s="93" t="n"/>
+      <c r="L4" s="89" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="127">
+      <c r="D5" s="223" t="n"/>
+      <c r="E5" s="63" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="I5" s="41" t="n"/>
+      <c r="I5" s="92" t="n"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="K5" s="49" t="inlineStr">
+      <c r="K5" s="64" t="inlineStr">
         <is>
           <t>RYR-SS-012</t>
         </is>
       </c>
-      <c r="L5" s="31" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="70">
-      <c r="D6" s="44" t="inlineStr">
+      <c r="L5" s="89" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="127">
+      <c r="D6" s="224" t="n"/>
+      <c r="E6" s="67" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="I6" s="41" t="n"/>
+      <c r="I6" s="92" t="n"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="K6" s="49" t="n">
+      <c r="K6" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="31" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="70">
-      <c r="D7" s="80" t="n"/>
-      <c r="E7" s="80" t="n"/>
-      <c r="F7" s="80" t="n"/>
-      <c r="G7" s="80" t="n"/>
-      <c r="H7" s="80" t="n"/>
-      <c r="I7" s="81" t="n"/>
+      <c r="L6" s="89" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="127">
+      <c r="D7" s="190" t="n"/>
+      <c r="E7" s="190" t="n"/>
+      <c r="F7" s="190" t="n"/>
+      <c r="G7" s="190" t="n"/>
+      <c r="H7" s="190" t="n"/>
+      <c r="I7" s="67" t="n"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="K7" s="49" t="inlineStr">
+      <c r="K7" s="64" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="L7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="70">
-      <c r="D8" s="66" t="n"/>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="66" t="n"/>
-      <c r="H8" s="66" t="n"/>
-      <c r="I8" s="81" t="n"/>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="L7" s="89" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="127">
+      <c r="D8" s="190" t="n"/>
+      <c r="E8" s="190" t="n"/>
+      <c r="F8" s="190" t="n"/>
+      <c r="G8" s="190" t="n"/>
+      <c r="H8" s="190" t="n"/>
+      <c r="I8" s="67" t="n"/>
+      <c r="J8" s="254" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="K8" s="49" t="inlineStr">
+      <c r="K8" s="58" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
-      <c r="L8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="70">
-      <c r="A9" s="103" t="inlineStr">
+      <c r="L8" s="94" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="127">
+      <c r="A9" s="255" t="inlineStr">
         <is>
           <t>Seguimiento de las acciones que salen de inspecciones, reportes, accidentes y auditorías · Decreto 1072 de 2015 · Resolución 0312 de 2019</t>
         </is>
       </c>
-      <c r="B9" s="115" t="n"/>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="115" t="n"/>
-      <c r="E9" s="115" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="115" t="n"/>
-      <c r="H9" s="115" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="115" t="n"/>
-      <c r="K9" s="115" t="n"/>
-      <c r="L9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="70">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="B9" s="349" t="n"/>
+      <c r="C9" s="349" t="n"/>
+      <c r="D9" s="349" t="n"/>
+      <c r="E9" s="349" t="n"/>
+      <c r="F9" s="349" t="n"/>
+      <c r="G9" s="349" t="n"/>
+      <c r="H9" s="349" t="n"/>
+      <c r="I9" s="349" t="n"/>
+      <c r="J9" s="349" t="n"/>
+      <c r="K9" s="349" t="n"/>
+      <c r="L9" s="351" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="127">
+      <c r="A10" s="137" t="inlineStr">
         <is>
           <t>1. DATOS DEL SEGUIMIENTO</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="38" t="n"/>
-      <c r="K10" s="38" t="n"/>
-      <c r="L10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1" s="70">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B10" s="98" t="n"/>
+      <c r="C10" s="98" t="n"/>
+      <c r="D10" s="98" t="n"/>
+      <c r="E10" s="98" t="n"/>
+      <c r="F10" s="98" t="n"/>
+      <c r="G10" s="98" t="n"/>
+      <c r="H10" s="98" t="n"/>
+      <c r="I10" s="98" t="n"/>
+      <c r="J10" s="98" t="n"/>
+      <c r="K10" s="98" t="n"/>
+      <c r="L10" s="97" t="n"/>
+    </row>
+    <row r="11" ht="19.05" customHeight="1" s="127">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="50" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="31" t="n"/>
-      <c r="I11" s="33" t="inlineStr">
+      <c r="B11" s="93" t="n"/>
+      <c r="C11" s="89" t="n"/>
+      <c r="D11" s="181" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="93" t="n"/>
+      <c r="H11" s="89" t="n"/>
+      <c r="I11" s="59" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
         </is>
       </c>
-      <c r="J11" s="31" t="n"/>
-      <c r="K11" s="48" t="n"/>
-      <c r="L11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="19" customHeight="1" s="70">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="J11" s="89" t="n"/>
+      <c r="K11" s="69" t="n"/>
+      <c r="L11" s="89" t="n"/>
+    </row>
+    <row r="12" ht="19.05" customHeight="1" s="127">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="43" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="31" t="n"/>
-      <c r="I12" s="33" t="inlineStr">
+      <c r="B12" s="93" t="n"/>
+      <c r="C12" s="89" t="n"/>
+      <c r="D12" s="68" t="n"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="F12" s="93" t="n"/>
+      <c r="G12" s="93" t="n"/>
+      <c r="H12" s="89" t="n"/>
+      <c r="I12" s="59" t="inlineStr">
         <is>
           <t>Periodo evaluado</t>
         </is>
       </c>
-      <c r="J12" s="31" t="n"/>
-      <c r="K12" s="48" t="n"/>
-      <c r="L12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1" s="70">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="J12" s="89" t="n"/>
+      <c r="K12" s="69" t="n"/>
+      <c r="L12" s="89" t="n"/>
+    </row>
+    <row r="13" ht="19.05" customHeight="1" s="127">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="43" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="31" t="n"/>
-      <c r="I13" s="33" t="inlineStr">
+      <c r="B13" s="93" t="n"/>
+      <c r="C13" s="89" t="n"/>
+      <c r="D13" s="68" t="n"/>
+      <c r="E13" s="93" t="n"/>
+      <c r="F13" s="93" t="n"/>
+      <c r="G13" s="93" t="n"/>
+      <c r="H13" s="89" t="n"/>
+      <c r="I13" s="59" t="inlineStr">
         <is>
           <t>Hoja N°</t>
         </is>
       </c>
-      <c r="J13" s="31" t="n"/>
-      <c r="K13" s="48" t="n"/>
-      <c r="L13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" s="70">
-      <c r="A14" s="54" t="inlineStr">
+      <c r="J13" s="89" t="n"/>
+      <c r="K13" s="69" t="n"/>
+      <c r="L13" s="89" t="n"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="127">
+      <c r="A14" s="137" t="inlineStr">
         <is>
           <t>2. REGISTRO DE ACCIONES</t>
         </is>
       </c>
-      <c r="B14" s="38" t="n"/>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="38" t="n"/>
-      <c r="I14" s="38" t="n"/>
-      <c r="J14" s="38" t="n"/>
-      <c r="K14" s="38" t="n"/>
-      <c r="L14" s="47" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="70">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="B14" s="98" t="n"/>
+      <c r="C14" s="98" t="n"/>
+      <c r="D14" s="98" t="n"/>
+      <c r="E14" s="98" t="n"/>
+      <c r="F14" s="98" t="n"/>
+      <c r="G14" s="98" t="n"/>
+      <c r="H14" s="98" t="n"/>
+      <c r="I14" s="98" t="n"/>
+      <c r="J14" s="98" t="n"/>
+      <c r="K14" s="98" t="n"/>
+      <c r="L14" s="97" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="127">
+      <c r="A15" s="184" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="184" t="inlineStr">
         <is>
           <t>Fecha de apertura</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="184" t="inlineStr">
         <is>
           <t>Origen</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D15" s="184" t="inlineStr">
         <is>
           <t>Referencia (N°)</t>
         </is>
       </c>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="E15" s="184" t="inlineStr">
         <is>
           <t>Hallazgo o causa</t>
         </is>
       </c>
-      <c r="F15" s="34" t="inlineStr">
+      <c r="F15" s="184" t="inlineStr">
         <is>
           <t>Tipo de acción</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="G15" s="184" t="inlineStr">
         <is>
           <t>Acción a ejecutar</t>
         </is>
       </c>
-      <c r="H15" s="34" t="inlineStr">
+      <c r="H15" s="184" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="I15" s="34" t="inlineStr">
+      <c r="I15" s="184" t="inlineStr">
         <is>
           <t>Fecha compromiso</t>
         </is>
       </c>
-      <c r="J15" s="34" t="inlineStr">
+      <c r="J15" s="184" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K15" s="34" t="inlineStr">
+      <c r="K15" s="184" t="inlineStr">
         <is>
           <t>Fecha de cierre</t>
         </is>
       </c>
-      <c r="L15" s="34" t="inlineStr">
+      <c r="L15" s="184" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="25" customHeight="1" s="70">
-      <c r="A16" s="57" t="n">
+    <row r="16" ht="25.05" customHeight="1" s="127">
+      <c r="A16" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="57" t="n"/>
-      <c r="C16" s="92" t="n"/>
-      <c r="D16" s="57" t="n"/>
-      <c r="E16" s="89" t="n"/>
-      <c r="F16" s="57" t="n"/>
-      <c r="G16" s="89" t="n"/>
-      <c r="H16" s="89" t="n"/>
-      <c r="I16" s="57" t="n"/>
-      <c r="J16" s="57" t="n"/>
-      <c r="K16" s="57" t="n"/>
-      <c r="L16" s="57" t="n"/>
-    </row>
-    <row r="17" ht="25" customHeight="1" s="70">
-      <c r="A17" s="57" t="n">
+      <c r="B16" s="126" t="n"/>
+      <c r="C16" s="75" t="n"/>
+      <c r="D16" s="126" t="n"/>
+      <c r="E16" s="72" t="n"/>
+      <c r="F16" s="126" t="n"/>
+      <c r="G16" s="72" t="n"/>
+      <c r="H16" s="72" t="n"/>
+      <c r="I16" s="126" t="n"/>
+      <c r="J16" s="126" t="n"/>
+      <c r="K16" s="126" t="n"/>
+      <c r="L16" s="126" t="n"/>
+    </row>
+    <row r="17" ht="25.05" customHeight="1" s="127">
+      <c r="A17" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="57" t="n"/>
-      <c r="C17" s="92" t="n"/>
-      <c r="D17" s="57" t="n"/>
-      <c r="E17" s="89" t="n"/>
-      <c r="F17" s="57" t="n"/>
-      <c r="G17" s="89" t="n"/>
-      <c r="H17" s="89" t="n"/>
-      <c r="I17" s="57" t="n"/>
-      <c r="J17" s="57" t="n"/>
-      <c r="K17" s="57" t="n"/>
-      <c r="L17" s="57" t="n"/>
-    </row>
-    <row r="18" ht="25" customHeight="1" s="70">
-      <c r="A18" s="57" t="n">
+      <c r="B17" s="126" t="n"/>
+      <c r="C17" s="75" t="n"/>
+      <c r="D17" s="126" t="n"/>
+      <c r="E17" s="72" t="n"/>
+      <c r="F17" s="126" t="n"/>
+      <c r="G17" s="72" t="n"/>
+      <c r="H17" s="72" t="n"/>
+      <c r="I17" s="126" t="n"/>
+      <c r="J17" s="126" t="n"/>
+      <c r="K17" s="126" t="n"/>
+      <c r="L17" s="126" t="n"/>
+    </row>
+    <row r="18" ht="25.05" customHeight="1" s="127">
+      <c r="A18" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="57" t="n"/>
-      <c r="C18" s="92" t="n"/>
-      <c r="D18" s="57" t="n"/>
-      <c r="E18" s="89" t="n"/>
-      <c r="F18" s="57" t="n"/>
-      <c r="G18" s="89" t="n"/>
-      <c r="H18" s="89" t="n"/>
-      <c r="I18" s="57" t="n"/>
-      <c r="J18" s="57" t="n"/>
-      <c r="K18" s="57" t="n"/>
-      <c r="L18" s="57" t="n"/>
-    </row>
-    <row r="19" ht="25" customHeight="1" s="70">
-      <c r="A19" s="57" t="n">
+      <c r="B18" s="126" t="n"/>
+      <c r="C18" s="75" t="n"/>
+      <c r="D18" s="126" t="n"/>
+      <c r="E18" s="72" t="n"/>
+      <c r="F18" s="126" t="n"/>
+      <c r="G18" s="72" t="n"/>
+      <c r="H18" s="72" t="n"/>
+      <c r="I18" s="126" t="n"/>
+      <c r="J18" s="126" t="n"/>
+      <c r="K18" s="126" t="n"/>
+      <c r="L18" s="126" t="n"/>
+    </row>
+    <row r="19" ht="25.05" customHeight="1" s="127">
+      <c r="A19" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="57" t="n"/>
-      <c r="C19" s="92" t="n"/>
-      <c r="D19" s="57" t="n"/>
-      <c r="E19" s="89" t="n"/>
-      <c r="F19" s="57" t="n"/>
-      <c r="G19" s="89" t="n"/>
-      <c r="H19" s="89" t="n"/>
-      <c r="I19" s="57" t="n"/>
-      <c r="J19" s="57" t="n"/>
-      <c r="K19" s="57" t="n"/>
-      <c r="L19" s="57" t="n"/>
-    </row>
-    <row r="20" ht="25" customHeight="1" s="70">
-      <c r="A20" s="57" t="n">
+      <c r="B19" s="126" t="n"/>
+      <c r="C19" s="75" t="n"/>
+      <c r="D19" s="126" t="n"/>
+      <c r="E19" s="72" t="n"/>
+      <c r="F19" s="126" t="n"/>
+      <c r="G19" s="72" t="n"/>
+      <c r="H19" s="72" t="n"/>
+      <c r="I19" s="126" t="n"/>
+      <c r="J19" s="126" t="n"/>
+      <c r="K19" s="126" t="n"/>
+      <c r="L19" s="126" t="n"/>
+    </row>
+    <row r="20" ht="25.05" customHeight="1" s="127">
+      <c r="A20" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="57" t="n"/>
-      <c r="C20" s="92" t="n"/>
-      <c r="D20" s="57" t="n"/>
-      <c r="E20" s="89" t="n"/>
-      <c r="F20" s="57" t="n"/>
-      <c r="G20" s="89" t="n"/>
-      <c r="H20" s="89" t="n"/>
-      <c r="I20" s="57" t="n"/>
-      <c r="J20" s="57" t="n"/>
-      <c r="K20" s="57" t="n"/>
-      <c r="L20" s="57" t="n"/>
-    </row>
-    <row r="21" ht="25" customHeight="1" s="70">
-      <c r="A21" s="57" t="n">
+      <c r="B20" s="126" t="n"/>
+      <c r="C20" s="75" t="n"/>
+      <c r="D20" s="126" t="n"/>
+      <c r="E20" s="72" t="n"/>
+      <c r="F20" s="126" t="n"/>
+      <c r="G20" s="72" t="n"/>
+      <c r="H20" s="72" t="n"/>
+      <c r="I20" s="126" t="n"/>
+      <c r="J20" s="126" t="n"/>
+      <c r="K20" s="126" t="n"/>
+      <c r="L20" s="126" t="n"/>
+    </row>
+    <row r="21" ht="25.05" customHeight="1" s="127">
+      <c r="A21" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="57" t="n"/>
-      <c r="C21" s="92" t="n"/>
-      <c r="D21" s="57" t="n"/>
-      <c r="E21" s="89" t="n"/>
-      <c r="F21" s="57" t="n"/>
-      <c r="G21" s="89" t="n"/>
-      <c r="H21" s="89" t="n"/>
-      <c r="I21" s="57" t="n"/>
-      <c r="J21" s="57" t="n"/>
-      <c r="K21" s="57" t="n"/>
-      <c r="L21" s="57" t="n"/>
-    </row>
-    <row r="22" ht="25" customHeight="1" s="70">
-      <c r="A22" s="57" t="n">
+      <c r="B21" s="126" t="n"/>
+      <c r="C21" s="75" t="n"/>
+      <c r="D21" s="126" t="n"/>
+      <c r="E21" s="72" t="n"/>
+      <c r="F21" s="126" t="n"/>
+      <c r="G21" s="72" t="n"/>
+      <c r="H21" s="72" t="n"/>
+      <c r="I21" s="126" t="n"/>
+      <c r="J21" s="126" t="n"/>
+      <c r="K21" s="126" t="n"/>
+      <c r="L21" s="126" t="n"/>
+    </row>
+    <row r="22" ht="25.05" customHeight="1" s="127">
+      <c r="A22" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="57" t="n"/>
-      <c r="C22" s="92" t="n"/>
-      <c r="D22" s="57" t="n"/>
-      <c r="E22" s="89" t="n"/>
-      <c r="F22" s="57" t="n"/>
-      <c r="G22" s="89" t="n"/>
-      <c r="H22" s="89" t="n"/>
-      <c r="I22" s="57" t="n"/>
-      <c r="J22" s="57" t="n"/>
-      <c r="K22" s="57" t="n"/>
-      <c r="L22" s="57" t="n"/>
-    </row>
-    <row r="23" ht="25" customHeight="1" s="70">
-      <c r="A23" s="57" t="n">
+      <c r="B22" s="126" t="n"/>
+      <c r="C22" s="75" t="n"/>
+      <c r="D22" s="126" t="n"/>
+      <c r="E22" s="72" t="n"/>
+      <c r="F22" s="126" t="n"/>
+      <c r="G22" s="72" t="n"/>
+      <c r="H22" s="72" t="n"/>
+      <c r="I22" s="126" t="n"/>
+      <c r="J22" s="126" t="n"/>
+      <c r="K22" s="126" t="n"/>
+      <c r="L22" s="126" t="n"/>
+    </row>
+    <row r="23" ht="25.05" customHeight="1" s="127">
+      <c r="A23" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="57" t="n"/>
-      <c r="C23" s="92" t="n"/>
-      <c r="D23" s="57" t="n"/>
-      <c r="E23" s="89" t="n"/>
-      <c r="F23" s="57" t="n"/>
-      <c r="G23" s="89" t="n"/>
-      <c r="H23" s="89" t="n"/>
-      <c r="I23" s="57" t="n"/>
-      <c r="J23" s="57" t="n"/>
-      <c r="K23" s="57" t="n"/>
-      <c r="L23" s="57" t="n"/>
-    </row>
-    <row r="24" ht="25" customHeight="1" s="70">
-      <c r="A24" s="57" t="n">
+      <c r="B23" s="126" t="n"/>
+      <c r="C23" s="75" t="n"/>
+      <c r="D23" s="126" t="n"/>
+      <c r="E23" s="72" t="n"/>
+      <c r="F23" s="126" t="n"/>
+      <c r="G23" s="72" t="n"/>
+      <c r="H23" s="72" t="n"/>
+      <c r="I23" s="126" t="n"/>
+      <c r="J23" s="126" t="n"/>
+      <c r="K23" s="126" t="n"/>
+      <c r="L23" s="126" t="n"/>
+    </row>
+    <row r="24" ht="25.05" customHeight="1" s="127">
+      <c r="A24" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="57" t="n"/>
-      <c r="C24" s="92" t="n"/>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="89" t="n"/>
-      <c r="F24" s="57" t="n"/>
-      <c r="G24" s="89" t="n"/>
-      <c r="H24" s="89" t="n"/>
-      <c r="I24" s="57" t="n"/>
-      <c r="J24" s="57" t="n"/>
-      <c r="K24" s="57" t="n"/>
-      <c r="L24" s="57" t="n"/>
-    </row>
-    <row r="25" ht="25" customHeight="1" s="70">
-      <c r="A25" s="57" t="n">
+      <c r="B24" s="126" t="n"/>
+      <c r="C24" s="75" t="n"/>
+      <c r="D24" s="126" t="n"/>
+      <c r="E24" s="72" t="n"/>
+      <c r="F24" s="126" t="n"/>
+      <c r="G24" s="72" t="n"/>
+      <c r="H24" s="72" t="n"/>
+      <c r="I24" s="126" t="n"/>
+      <c r="J24" s="126" t="n"/>
+      <c r="K24" s="126" t="n"/>
+      <c r="L24" s="126" t="n"/>
+    </row>
+    <row r="25" ht="25.05" customHeight="1" s="127">
+      <c r="A25" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="57" t="n"/>
-      <c r="C25" s="92" t="n"/>
-      <c r="D25" s="57" t="n"/>
-      <c r="E25" s="89" t="n"/>
-      <c r="F25" s="57" t="n"/>
-      <c r="G25" s="89" t="n"/>
-      <c r="H25" s="89" t="n"/>
-      <c r="I25" s="57" t="n"/>
-      <c r="J25" s="57" t="n"/>
-      <c r="K25" s="57" t="n"/>
-      <c r="L25" s="57" t="n"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" s="70">
-      <c r="A26" s="54" t="inlineStr">
+      <c r="B25" s="126" t="n"/>
+      <c r="C25" s="75" t="n"/>
+      <c r="D25" s="126" t="n"/>
+      <c r="E25" s="72" t="n"/>
+      <c r="F25" s="126" t="n"/>
+      <c r="G25" s="72" t="n"/>
+      <c r="H25" s="72" t="n"/>
+      <c r="I25" s="126" t="n"/>
+      <c r="J25" s="126" t="n"/>
+      <c r="K25" s="126" t="n"/>
+      <c r="L25" s="126" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="127">
+      <c r="A26" s="137" t="inlineStr">
         <is>
           <t>3. RESUMEN DE ESTA HOJA</t>
         </is>
       </c>
-      <c r="B26" s="38" t="n"/>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="38" t="n"/>
-      <c r="E26" s="38" t="n"/>
-      <c r="F26" s="38" t="n"/>
-      <c r="G26" s="38" t="n"/>
-      <c r="H26" s="38" t="n"/>
-      <c r="I26" s="38" t="n"/>
-      <c r="J26" s="38" t="n"/>
-      <c r="K26" s="38" t="n"/>
-      <c r="L26" s="47" t="n"/>
-    </row>
-    <row r="27" ht="19" customHeight="1" s="70">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="B26" s="98" t="n"/>
+      <c r="C26" s="98" t="n"/>
+      <c r="D26" s="98" t="n"/>
+      <c r="E26" s="98" t="n"/>
+      <c r="F26" s="98" t="n"/>
+      <c r="G26" s="98" t="n"/>
+      <c r="H26" s="98" t="n"/>
+      <c r="I26" s="98" t="n"/>
+      <c r="J26" s="98" t="n"/>
+      <c r="K26" s="98" t="n"/>
+      <c r="L26" s="97" t="n"/>
+    </row>
+    <row r="27" ht="19.05" customHeight="1" s="127">
+      <c r="A27" s="154" t="inlineStr">
         <is>
           <t>Total de acciones</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="B27" s="89" t="n"/>
+      <c r="C27" s="154" t="inlineStr">
         <is>
           <t>Abiertas</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D27" s="154" t="inlineStr">
         <is>
           <t>En proceso</t>
         </is>
       </c>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="34" t="inlineStr">
+      <c r="E27" s="89" t="n"/>
+      <c r="F27" s="154" t="inlineStr">
         <is>
           <t>Cerradas</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
+      <c r="G27" s="154" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="H27" s="34" t="inlineStr">
+      <c r="H27" s="154" t="inlineStr">
         <is>
           <t>% de cierre</t>
         </is>
       </c>
-      <c r="I27" s="34" t="inlineStr">
+      <c r="I27" s="154" t="inlineStr">
         <is>
           <t>Eficaces</t>
         </is>
       </c>
-      <c r="J27" s="31" t="n"/>
-      <c r="K27" s="34" t="inlineStr">
+      <c r="J27" s="89" t="n"/>
+      <c r="K27" s="154" t="inlineStr">
         <is>
           <t>% de eficacia</t>
         </is>
       </c>
-      <c r="L27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="21" customHeight="1" s="70">
-      <c r="A28" s="58">
+      <c r="L27" s="89" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1" s="127">
+      <c r="A28" s="328">
         <f>COUNTA(E16:E25)</f>
         <v/>
       </c>
-      <c r="B28" s="31" t="n"/>
-      <c r="C28" s="58">
+      <c r="B28" s="94" t="n"/>
+      <c r="C28" s="328">
         <f>COUNTIF(J16:J25,"Abierta")</f>
         <v/>
       </c>
-      <c r="D28" s="58">
+      <c r="D28" s="328">
         <f>COUNTIF(J16:J25,"En proceso")</f>
         <v/>
       </c>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="58">
+      <c r="E28" s="94" t="n"/>
+      <c r="F28" s="328">
         <f>COUNTIF(J16:J25,"Cerrada")</f>
         <v/>
       </c>
-      <c r="G28" s="58">
+      <c r="G28" s="328">
         <f>COUNTIF(J16:J25,"Vencida")</f>
         <v/>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="330">
         <f>IFERROR(F28/A28,"")</f>
         <v/>
       </c>
-      <c r="I28" s="58">
+      <c r="I28" s="328">
         <f>COUNTIF(L16:L25,"Eficaz")</f>
         <v/>
       </c>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="32">
+      <c r="J28" s="94" t="n"/>
+      <c r="K28" s="330">
         <f>IFERROR(I28/F28,"")</f>
         <v/>
       </c>
-      <c r="L28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="16" customHeight="1" s="70">
-      <c r="A29" s="103" t="inlineStr">
+      <c r="L28" s="94" t="n"/>
+    </row>
+    <row r="29" ht="16.05" customHeight="1" s="127">
+      <c r="A29" s="255" t="inlineStr">
         <is>
           <t>% de cierre = Cerradas ÷ Total · % de eficacia = Eficaces ÷ Cerradas. Una acción cerrada se verifica: si no resolvió el problema se marca "No eficaz" y se abre una nueva.</t>
         </is>
       </c>
-      <c r="B29" s="115" t="n"/>
-      <c r="C29" s="115" t="n"/>
-      <c r="D29" s="115" t="n"/>
-      <c r="E29" s="115" t="n"/>
-      <c r="F29" s="115" t="n"/>
-      <c r="G29" s="115" t="n"/>
-      <c r="H29" s="115" t="n"/>
-      <c r="I29" s="115" t="n"/>
-      <c r="J29" s="115" t="n"/>
-      <c r="K29" s="115" t="n"/>
-      <c r="L29" s="116" t="n"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" s="70">
-      <c r="A30" s="54" t="inlineStr">
+      <c r="B29" s="349" t="n"/>
+      <c r="C29" s="349" t="n"/>
+      <c r="D29" s="349" t="n"/>
+      <c r="E29" s="349" t="n"/>
+      <c r="F29" s="349" t="n"/>
+      <c r="G29" s="349" t="n"/>
+      <c r="H29" s="349" t="n"/>
+      <c r="I29" s="349" t="n"/>
+      <c r="J29" s="349" t="n"/>
+      <c r="K29" s="349" t="n"/>
+      <c r="L29" s="351" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="127">
+      <c r="A30" s="227" t="inlineStr">
         <is>
           <t>4. FIRMAS</t>
         </is>
       </c>
-      <c r="B30" s="38" t="n"/>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="38" t="n"/>
-      <c r="E30" s="38" t="n"/>
-      <c r="F30" s="38" t="n"/>
-      <c r="G30" s="38" t="n"/>
-      <c r="H30" s="38" t="n"/>
-      <c r="I30" s="38" t="n"/>
-      <c r="J30" s="38" t="n"/>
-      <c r="K30" s="38" t="n"/>
-      <c r="L30" s="47" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" s="70">
-      <c r="A31" s="51" t="inlineStr">
+      <c r="L30" s="92" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="127">
+      <c r="A31" s="263" t="inlineStr">
         <is>
           <t>ELABORÓ — RESPONSABLE SST</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n"/>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="51" t="inlineStr">
+      <c r="B31" s="347" t="n"/>
+      <c r="C31" s="347" t="n"/>
+      <c r="D31" s="348" t="n"/>
+      <c r="E31" s="263" t="inlineStr">
         <is>
           <t>REVISÓ — RESIDENTE DE OBRA</t>
         </is>
       </c>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="30" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="51" t="inlineStr">
+      <c r="F31" s="347" t="n"/>
+      <c r="G31" s="347" t="n"/>
+      <c r="H31" s="348" t="n"/>
+      <c r="I31" s="263" t="inlineStr">
         <is>
           <t>Vo.Bo. — GERENCIA / INTERVENTORÍA</t>
         </is>
       </c>
-      <c r="J31" s="30" t="n"/>
-      <c r="K31" s="30" t="n"/>
-      <c r="L31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="42" customHeight="1" s="70">
-      <c r="A32" s="39" t="inlineStr">
+      <c r="J31" s="347" t="n"/>
+      <c r="K31" s="347" t="n"/>
+      <c r="L31" s="348" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1" s="127">
+      <c r="A32" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="43" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="39" t="inlineStr">
+      <c r="B32" s="97" t="n"/>
+      <c r="C32" s="301" t="n"/>
+      <c r="D32" s="97" t="n"/>
+      <c r="E32" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="43" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="39" t="inlineStr">
+      <c r="F32" s="97" t="n"/>
+      <c r="G32" s="301" t="n"/>
+      <c r="H32" s="97" t="n"/>
+      <c r="I32" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="43" t="n"/>
-      <c r="L32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="21" customHeight="1" s="70">
-      <c r="A33" s="39" t="inlineStr">
+      <c r="J32" s="97" t="n"/>
+      <c r="K32" s="301" t="n"/>
+      <c r="L32" s="97" t="n"/>
+    </row>
+    <row r="33" ht="21" customHeight="1" s="127">
+      <c r="A33" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="39" t="inlineStr">
+      <c r="B33" s="89" t="n"/>
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="89" t="n"/>
+      <c r="E33" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="43" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="39" t="inlineStr">
+      <c r="F33" s="89" t="n"/>
+      <c r="G33" s="68" t="n"/>
+      <c r="H33" s="89" t="n"/>
+      <c r="I33" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="43" t="n"/>
-      <c r="L33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="21" customHeight="1" s="70">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="J33" s="89" t="n"/>
+      <c r="K33" s="68" t="n"/>
+      <c r="L33" s="89" t="n"/>
+    </row>
+    <row r="34" ht="21" customHeight="1" s="127">
+      <c r="A34" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B34" s="31" t="n"/>
-      <c r="C34" s="43" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="39" t="inlineStr">
+      <c r="B34" s="89" t="n"/>
+      <c r="C34" s="68" t="n"/>
+      <c r="D34" s="89" t="n"/>
+      <c r="E34" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="43" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="39" t="inlineStr">
+      <c r="F34" s="89" t="n"/>
+      <c r="G34" s="68" t="n"/>
+      <c r="H34" s="89" t="n"/>
+      <c r="I34" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="43" t="n"/>
-      <c r="L34" s="31" t="n"/>
+      <c r="J34" s="89" t="n"/>
+      <c r="K34" s="68" t="n"/>
+      <c r="L34" s="89" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="61" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="G35" s="63">
+      <c r="G35" s="105">
         <f>K5</f>
         <v/>
       </c>
@@ -2014,6 +3156,7 @@
   <mergeCells count="57">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="I34:J34"/>
+    <mergeCell ref="E3:L3"/>
     <mergeCell ref="K34:L34"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="E33:F33"/>
@@ -2021,12 +3164,12 @@
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="I27:J27"/>
+    <mergeCell ref="E5:I5"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="D1:L2"/>
     <mergeCell ref="I31:L31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="D27:E27"/>
@@ -2034,7 +3177,6 @@
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="A14:L14"/>
-    <mergeCell ref="D3:L3"/>
     <mergeCell ref="G35:L35"/>
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="A27:B27"/>
@@ -2044,9 +3186,9 @@
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="A29:L29"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="K8:L8"/>
     <mergeCell ref="G34:H34"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="D5:I5"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
@@ -2063,15 +3205,15 @@
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="A28:B28"/>
+    <mergeCell ref="E1:L2"/>
     <mergeCell ref="K28:L28"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="D6:I6"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 Página &amp;P de &amp;N</oddFooter>

--- a/public/plantilla-acciones-correctivas.xlsx
+++ b/public/plantilla-acciones-correctivas.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones Correctivas" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="39">
+  <numFmts count="0"/>
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -296,6 +297,10 @@
       <color rgb="FF0B1F33"/>
       <sz val="9"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1024,7 +1029,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1928,6 +1933,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2611,19 +2648,19 @@
       </c>
       <c r="B11" s="93" t="n"/>
       <c r="C11" s="89" t="n"/>
-      <c r="D11" s="181" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="89" t="n"/>
+      <c r="D11" s="360" t="n"/>
+      <c r="E11" s="361" t="n"/>
+      <c r="F11" s="361" t="n"/>
+      <c r="G11" s="361" t="n"/>
+      <c r="H11" s="362" t="n"/>
       <c r="I11" s="59" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
         </is>
       </c>
       <c r="J11" s="89" t="n"/>
-      <c r="K11" s="69" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="K11" s="363" t="n"/>
+      <c r="L11" s="362" t="n"/>
     </row>
     <row r="12" ht="19.05" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2633,19 +2670,19 @@
       </c>
       <c r="B12" s="93" t="n"/>
       <c r="C12" s="89" t="n"/>
-      <c r="D12" s="68" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="93" t="n"/>
-      <c r="H12" s="89" t="n"/>
+      <c r="D12" s="364" t="n"/>
+      <c r="E12" s="361" t="n"/>
+      <c r="F12" s="361" t="n"/>
+      <c r="G12" s="361" t="n"/>
+      <c r="H12" s="362" t="n"/>
       <c r="I12" s="59" t="inlineStr">
         <is>
           <t>Periodo evaluado</t>
         </is>
       </c>
       <c r="J12" s="89" t="n"/>
-      <c r="K12" s="69" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="K12" s="363" t="n"/>
+      <c r="L12" s="362" t="n"/>
     </row>
     <row r="13" ht="19.05" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2655,19 +2692,19 @@
       </c>
       <c r="B13" s="93" t="n"/>
       <c r="C13" s="89" t="n"/>
-      <c r="D13" s="68" t="n"/>
-      <c r="E13" s="93" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="93" t="n"/>
-      <c r="H13" s="89" t="n"/>
+      <c r="D13" s="364" t="n"/>
+      <c r="E13" s="361" t="n"/>
+      <c r="F13" s="361" t="n"/>
+      <c r="G13" s="361" t="n"/>
+      <c r="H13" s="362" t="n"/>
       <c r="I13" s="59" t="inlineStr">
         <is>
           <t>Hoja N°</t>
         </is>
       </c>
       <c r="J13" s="89" t="n"/>
-      <c r="K13" s="69" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="K13" s="363" t="n"/>
+      <c r="L13" s="362" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="127">
       <c r="A14" s="137" t="inlineStr">
@@ -2750,164 +2787,164 @@
       </c>
     </row>
     <row r="16" ht="25.05" customHeight="1" s="127">
-      <c r="A16" s="126" t="n">
+      <c r="A16" s="365" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="126" t="n"/>
-      <c r="C16" s="75" t="n"/>
-      <c r="D16" s="126" t="n"/>
-      <c r="E16" s="72" t="n"/>
-      <c r="F16" s="126" t="n"/>
-      <c r="G16" s="72" t="n"/>
-      <c r="H16" s="72" t="n"/>
-      <c r="I16" s="126" t="n"/>
-      <c r="J16" s="126" t="n"/>
-      <c r="K16" s="126" t="n"/>
-      <c r="L16" s="126" t="n"/>
+      <c r="B16" s="366" t="n"/>
+      <c r="C16" s="363" t="n"/>
+      <c r="D16" s="366" t="n"/>
+      <c r="E16" s="364" t="n"/>
+      <c r="F16" s="366" t="n"/>
+      <c r="G16" s="364" t="n"/>
+      <c r="H16" s="364" t="n"/>
+      <c r="I16" s="366" t="n"/>
+      <c r="J16" s="366" t="n"/>
+      <c r="K16" s="366" t="n"/>
+      <c r="L16" s="366" t="n"/>
     </row>
     <row r="17" ht="25.05" customHeight="1" s="127">
-      <c r="A17" s="126" t="n">
+      <c r="A17" s="365" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="126" t="n"/>
-      <c r="C17" s="75" t="n"/>
-      <c r="D17" s="126" t="n"/>
-      <c r="E17" s="72" t="n"/>
-      <c r="F17" s="126" t="n"/>
-      <c r="G17" s="72" t="n"/>
-      <c r="H17" s="72" t="n"/>
-      <c r="I17" s="126" t="n"/>
-      <c r="J17" s="126" t="n"/>
-      <c r="K17" s="126" t="n"/>
-      <c r="L17" s="126" t="n"/>
+      <c r="B17" s="366" t="n"/>
+      <c r="C17" s="363" t="n"/>
+      <c r="D17" s="366" t="n"/>
+      <c r="E17" s="364" t="n"/>
+      <c r="F17" s="366" t="n"/>
+      <c r="G17" s="364" t="n"/>
+      <c r="H17" s="364" t="n"/>
+      <c r="I17" s="366" t="n"/>
+      <c r="J17" s="366" t="n"/>
+      <c r="K17" s="366" t="n"/>
+      <c r="L17" s="366" t="n"/>
     </row>
     <row r="18" ht="25.05" customHeight="1" s="127">
-      <c r="A18" s="126" t="n">
+      <c r="A18" s="365" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="126" t="n"/>
-      <c r="C18" s="75" t="n"/>
-      <c r="D18" s="126" t="n"/>
-      <c r="E18" s="72" t="n"/>
-      <c r="F18" s="126" t="n"/>
-      <c r="G18" s="72" t="n"/>
-      <c r="H18" s="72" t="n"/>
-      <c r="I18" s="126" t="n"/>
-      <c r="J18" s="126" t="n"/>
-      <c r="K18" s="126" t="n"/>
-      <c r="L18" s="126" t="n"/>
+      <c r="B18" s="366" t="n"/>
+      <c r="C18" s="363" t="n"/>
+      <c r="D18" s="366" t="n"/>
+      <c r="E18" s="364" t="n"/>
+      <c r="F18" s="366" t="n"/>
+      <c r="G18" s="364" t="n"/>
+      <c r="H18" s="364" t="n"/>
+      <c r="I18" s="366" t="n"/>
+      <c r="J18" s="366" t="n"/>
+      <c r="K18" s="366" t="n"/>
+      <c r="L18" s="366" t="n"/>
     </row>
     <row r="19" ht="25.05" customHeight="1" s="127">
-      <c r="A19" s="126" t="n">
+      <c r="A19" s="365" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="126" t="n"/>
-      <c r="C19" s="75" t="n"/>
-      <c r="D19" s="126" t="n"/>
-      <c r="E19" s="72" t="n"/>
-      <c r="F19" s="126" t="n"/>
-      <c r="G19" s="72" t="n"/>
-      <c r="H19" s="72" t="n"/>
-      <c r="I19" s="126" t="n"/>
-      <c r="J19" s="126" t="n"/>
-      <c r="K19" s="126" t="n"/>
-      <c r="L19" s="126" t="n"/>
+      <c r="B19" s="366" t="n"/>
+      <c r="C19" s="363" t="n"/>
+      <c r="D19" s="366" t="n"/>
+      <c r="E19" s="364" t="n"/>
+      <c r="F19" s="366" t="n"/>
+      <c r="G19" s="364" t="n"/>
+      <c r="H19" s="364" t="n"/>
+      <c r="I19" s="366" t="n"/>
+      <c r="J19" s="366" t="n"/>
+      <c r="K19" s="366" t="n"/>
+      <c r="L19" s="366" t="n"/>
     </row>
     <row r="20" ht="25.05" customHeight="1" s="127">
-      <c r="A20" s="126" t="n">
+      <c r="A20" s="365" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="126" t="n"/>
-      <c r="C20" s="75" t="n"/>
-      <c r="D20" s="126" t="n"/>
-      <c r="E20" s="72" t="n"/>
-      <c r="F20" s="126" t="n"/>
-      <c r="G20" s="72" t="n"/>
-      <c r="H20" s="72" t="n"/>
-      <c r="I20" s="126" t="n"/>
-      <c r="J20" s="126" t="n"/>
-      <c r="K20" s="126" t="n"/>
-      <c r="L20" s="126" t="n"/>
+      <c r="B20" s="366" t="n"/>
+      <c r="C20" s="363" t="n"/>
+      <c r="D20" s="366" t="n"/>
+      <c r="E20" s="364" t="n"/>
+      <c r="F20" s="366" t="n"/>
+      <c r="G20" s="364" t="n"/>
+      <c r="H20" s="364" t="n"/>
+      <c r="I20" s="366" t="n"/>
+      <c r="J20" s="366" t="n"/>
+      <c r="K20" s="366" t="n"/>
+      <c r="L20" s="366" t="n"/>
     </row>
     <row r="21" ht="25.05" customHeight="1" s="127">
-      <c r="A21" s="126" t="n">
+      <c r="A21" s="365" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="126" t="n"/>
-      <c r="C21" s="75" t="n"/>
-      <c r="D21" s="126" t="n"/>
-      <c r="E21" s="72" t="n"/>
-      <c r="F21" s="126" t="n"/>
-      <c r="G21" s="72" t="n"/>
-      <c r="H21" s="72" t="n"/>
-      <c r="I21" s="126" t="n"/>
-      <c r="J21" s="126" t="n"/>
-      <c r="K21" s="126" t="n"/>
-      <c r="L21" s="126" t="n"/>
+      <c r="B21" s="366" t="n"/>
+      <c r="C21" s="363" t="n"/>
+      <c r="D21" s="366" t="n"/>
+      <c r="E21" s="364" t="n"/>
+      <c r="F21" s="366" t="n"/>
+      <c r="G21" s="364" t="n"/>
+      <c r="H21" s="364" t="n"/>
+      <c r="I21" s="366" t="n"/>
+      <c r="J21" s="366" t="n"/>
+      <c r="K21" s="366" t="n"/>
+      <c r="L21" s="366" t="n"/>
     </row>
     <row r="22" ht="25.05" customHeight="1" s="127">
-      <c r="A22" s="126" t="n">
+      <c r="A22" s="365" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="126" t="n"/>
-      <c r="C22" s="75" t="n"/>
-      <c r="D22" s="126" t="n"/>
-      <c r="E22" s="72" t="n"/>
-      <c r="F22" s="126" t="n"/>
-      <c r="G22" s="72" t="n"/>
-      <c r="H22" s="72" t="n"/>
-      <c r="I22" s="126" t="n"/>
-      <c r="J22" s="126" t="n"/>
-      <c r="K22" s="126" t="n"/>
-      <c r="L22" s="126" t="n"/>
+      <c r="B22" s="366" t="n"/>
+      <c r="C22" s="363" t="n"/>
+      <c r="D22" s="366" t="n"/>
+      <c r="E22" s="364" t="n"/>
+      <c r="F22" s="366" t="n"/>
+      <c r="G22" s="364" t="n"/>
+      <c r="H22" s="364" t="n"/>
+      <c r="I22" s="366" t="n"/>
+      <c r="J22" s="366" t="n"/>
+      <c r="K22" s="366" t="n"/>
+      <c r="L22" s="366" t="n"/>
     </row>
     <row r="23" ht="25.05" customHeight="1" s="127">
-      <c r="A23" s="126" t="n">
+      <c r="A23" s="365" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="126" t="n"/>
-      <c r="C23" s="75" t="n"/>
-      <c r="D23" s="126" t="n"/>
-      <c r="E23" s="72" t="n"/>
-      <c r="F23" s="126" t="n"/>
-      <c r="G23" s="72" t="n"/>
-      <c r="H23" s="72" t="n"/>
-      <c r="I23" s="126" t="n"/>
-      <c r="J23" s="126" t="n"/>
-      <c r="K23" s="126" t="n"/>
-      <c r="L23" s="126" t="n"/>
+      <c r="B23" s="366" t="n"/>
+      <c r="C23" s="363" t="n"/>
+      <c r="D23" s="366" t="n"/>
+      <c r="E23" s="364" t="n"/>
+      <c r="F23" s="366" t="n"/>
+      <c r="G23" s="364" t="n"/>
+      <c r="H23" s="364" t="n"/>
+      <c r="I23" s="366" t="n"/>
+      <c r="J23" s="366" t="n"/>
+      <c r="K23" s="366" t="n"/>
+      <c r="L23" s="366" t="n"/>
     </row>
     <row r="24" ht="25.05" customHeight="1" s="127">
-      <c r="A24" s="126" t="n">
+      <c r="A24" s="365" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="126" t="n"/>
-      <c r="C24" s="75" t="n"/>
-      <c r="D24" s="126" t="n"/>
-      <c r="E24" s="72" t="n"/>
-      <c r="F24" s="126" t="n"/>
-      <c r="G24" s="72" t="n"/>
-      <c r="H24" s="72" t="n"/>
-      <c r="I24" s="126" t="n"/>
-      <c r="J24" s="126" t="n"/>
-      <c r="K24" s="126" t="n"/>
-      <c r="L24" s="126" t="n"/>
+      <c r="B24" s="366" t="n"/>
+      <c r="C24" s="363" t="n"/>
+      <c r="D24" s="366" t="n"/>
+      <c r="E24" s="364" t="n"/>
+      <c r="F24" s="366" t="n"/>
+      <c r="G24" s="364" t="n"/>
+      <c r="H24" s="364" t="n"/>
+      <c r="I24" s="366" t="n"/>
+      <c r="J24" s="366" t="n"/>
+      <c r="K24" s="366" t="n"/>
+      <c r="L24" s="366" t="n"/>
     </row>
     <row r="25" ht="25.05" customHeight="1" s="127">
-      <c r="A25" s="126" t="n">
+      <c r="A25" s="365" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="126" t="n"/>
-      <c r="C25" s="75" t="n"/>
-      <c r="D25" s="126" t="n"/>
-      <c r="E25" s="72" t="n"/>
-      <c r="F25" s="126" t="n"/>
-      <c r="G25" s="72" t="n"/>
-      <c r="H25" s="72" t="n"/>
-      <c r="I25" s="126" t="n"/>
-      <c r="J25" s="126" t="n"/>
-      <c r="K25" s="126" t="n"/>
-      <c r="L25" s="126" t="n"/>
+      <c r="B25" s="366" t="n"/>
+      <c r="C25" s="363" t="n"/>
+      <c r="D25" s="366" t="n"/>
+      <c r="E25" s="364" t="n"/>
+      <c r="F25" s="366" t="n"/>
+      <c r="G25" s="364" t="n"/>
+      <c r="H25" s="364" t="n"/>
+      <c r="I25" s="366" t="n"/>
+      <c r="J25" s="366" t="n"/>
+      <c r="K25" s="366" t="n"/>
+      <c r="L25" s="366" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="127">
       <c r="A26" s="137" t="inlineStr">
@@ -3070,24 +3107,24 @@
         </is>
       </c>
       <c r="B32" s="97" t="n"/>
-      <c r="C32" s="301" t="n"/>
-      <c r="D32" s="97" t="n"/>
+      <c r="C32" s="367" t="n"/>
+      <c r="D32" s="368" t="n"/>
       <c r="E32" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F32" s="97" t="n"/>
-      <c r="G32" s="301" t="n"/>
-      <c r="H32" s="97" t="n"/>
+      <c r="G32" s="367" t="n"/>
+      <c r="H32" s="368" t="n"/>
       <c r="I32" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J32" s="97" t="n"/>
-      <c r="K32" s="301" t="n"/>
-      <c r="L32" s="97" t="n"/>
+      <c r="K32" s="367" t="n"/>
+      <c r="L32" s="368" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="127">
       <c r="A33" s="70" t="inlineStr">
@@ -3096,24 +3133,24 @@
         </is>
       </c>
       <c r="B33" s="89" t="n"/>
-      <c r="C33" s="68" t="n"/>
-      <c r="D33" s="89" t="n"/>
+      <c r="C33" s="364" t="n"/>
+      <c r="D33" s="362" t="n"/>
       <c r="E33" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F33" s="89" t="n"/>
-      <c r="G33" s="68" t="n"/>
-      <c r="H33" s="89" t="n"/>
+      <c r="G33" s="364" t="n"/>
+      <c r="H33" s="362" t="n"/>
       <c r="I33" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J33" s="89" t="n"/>
-      <c r="K33" s="68" t="n"/>
-      <c r="L33" s="89" t="n"/>
+      <c r="K33" s="364" t="n"/>
+      <c r="L33" s="362" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1" s="127">
       <c r="A34" s="70" t="inlineStr">
@@ -3122,24 +3159,24 @@
         </is>
       </c>
       <c r="B34" s="89" t="n"/>
-      <c r="C34" s="68" t="n"/>
-      <c r="D34" s="89" t="n"/>
+      <c r="C34" s="364" t="n"/>
+      <c r="D34" s="362" t="n"/>
       <c r="E34" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F34" s="89" t="n"/>
-      <c r="G34" s="68" t="n"/>
-      <c r="H34" s="89" t="n"/>
+      <c r="G34" s="364" t="n"/>
+      <c r="H34" s="362" t="n"/>
       <c r="I34" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J34" s="89" t="n"/>
-      <c r="K34" s="68" t="n"/>
-      <c r="L34" s="89" t="n"/>
+      <c r="K34" s="364" t="n"/>
+      <c r="L34" s="362" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="25" t="inlineStr">
@@ -3153,6 +3190,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="57">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="I34:J34"/>
